--- a/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_クロス集計設計書_20260805.xlsx
+++ b/小野町_引継ぎ_整理済/14_アンケート集計/小野町_令和7年度調査_クロス集計設計書_20260805.xlsx
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>【最重要論点】認定率は県内2位・全国比1.24倍だが給付月額は県内中位。調整後認定率の地域差指数1.24に対し受給率は1.07</t>
+          <t>【最重要論点】認定率は全国比1.24倍と高いが給付月額は県内中位。調整後認定率の地域差指数1.24に対し受給率は1.07</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
